--- a/table/resources/sample/RoomExpend.xlsx
+++ b/table/resources/sample/RoomExpend.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="RoomExpend" sheetId="1" r:id="rId1"/>
@@ -1149,7 +1149,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="2">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>11</v>
@@ -1209,7 +1209,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="3">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>11</v>

--- a/table/resources/sample/RoomExpend.xlsx
+++ b/table/resources/sample/RoomExpend.xlsx
@@ -98,16 +98,16 @@
     <t>requiredItem</t>
   </si>
   <si>
-    <t>1980000:10</t>
-  </si>
-  <si>
-    <t>1980000:20</t>
-  </si>
-  <si>
-    <t>1980000:40</t>
-  </si>
-  <si>
-    <t>1980000:80</t>
+    <t>1980000:100</t>
+  </si>
+  <si>
+    <t>1980000:180</t>
+  </si>
+  <si>
+    <t>1980000:320</t>
+  </si>
+  <si>
+    <t>1980000:560</t>
   </si>
   <si>
     <t>1020001:1</t>

--- a/table/resources/sample/RoomExpend.xlsx
+++ b/table/resources/sample/RoomExpend.xlsx
@@ -98,16 +98,16 @@
     <t>requiredItem</t>
   </si>
   <si>
-    <t>1980000:100</t>
-  </si>
-  <si>
-    <t>1980000:180</t>
-  </si>
-  <si>
-    <t>1980000:320</t>
-  </si>
-  <si>
-    <t>1980000:560</t>
+    <t>1980000:10</t>
+  </si>
+  <si>
+    <t>1980000:20</t>
+  </si>
+  <si>
+    <t>1980000:40</t>
+  </si>
+  <si>
+    <t>1980000:80</t>
   </si>
   <si>
     <t>1020001:1</t>

--- a/table/resources/sample/RoomExpend.xlsx
+++ b/table/resources/sample/RoomExpend.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="RoomExpend" sheetId="1" r:id="rId1"/>
@@ -58,12 +58,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+为空时，不展示
+有货币内容时，前端展示原价并添加删除线
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
   <si>
     <t>id</t>
   </si>
@@ -80,6 +104,9 @@
     <t>消耗道具</t>
   </si>
   <si>
+    <t>打折原价展示</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -98,16 +125,13 @@
     <t>requiredItem</t>
   </si>
   <si>
-    <t>1980000:100</t>
-  </si>
-  <si>
-    <t>1980000:180</t>
-  </si>
-  <si>
-    <t>1980000:320</t>
-  </si>
-  <si>
-    <t>1980000:560</t>
+    <t>initialPrice</t>
+  </si>
+  <si>
+    <t>client</t>
+  </si>
+  <si>
+    <t>1980000:0</t>
   </si>
   <si>
     <t>1020001:1</t>
@@ -132,13 +156,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -296,12 +326,24 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -628,76 +670,70 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -706,10 +742,10 @@
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -718,10 +754,10 @@
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -730,10 +766,10 @@
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -742,10 +778,10 @@
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -754,21 +790,33 @@
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1082,15 +1130,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="13.75" customWidth="1"/>
     <col min="4" max="4" width="15.75" customWidth="1"/>
     <col min="5" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1106,167 +1155,205 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="4" ht="16.5" spans="1:6">
+      <c r="F4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="4">
         <v>2</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="4">
         <v>60</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2"/>
+      <c r="D5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4">
+        <v>100</v>
+      </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>2</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="4">
         <v>2</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="4">
         <v>120</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="2"/>
+      <c r="D6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4">
+        <v>180</v>
+      </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>3</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="4">
         <v>2</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="4">
         <v>240</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="2"/>
+      <c r="D7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4">
+        <v>320</v>
+      </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>4</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="4">
         <v>480</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4">
+        <v>560</v>
+      </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>17</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="5">
         <v>1</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
         <v>60</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="D9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>15</v>
       </c>
+      <c r="F9" s="5">
+        <v>100</v>
+      </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>18</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="5">
         <v>1</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>120</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="D10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>16</v>
       </c>
+      <c r="F10" s="5">
+        <v>180</v>
+      </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>19</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="5">
         <v>1</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>240</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="D11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="F11" s="5">
+        <v>320</v>
+      </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>20</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="5">
         <v>1</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>480</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="5" t="s">
         <v>18</v>
+      </c>
+      <c r="F12" s="5">
+        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/table/resources/sample/RoomExpend.xlsx
+++ b/table/resources/sample/RoomExpend.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="RoomExpend" sheetId="1" r:id="rId1"/>
@@ -58,12 +58,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+为空时，不展示
+有货币内容时，前端展示原价并添加删除线
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
   <si>
     <t>id</t>
   </si>
@@ -80,6 +104,9 @@
     <t>消耗道具</t>
   </si>
   <si>
+    <t>打折原价展示</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -98,16 +125,13 @@
     <t>requiredItem</t>
   </si>
   <si>
-    <t>1980000:10</t>
-  </si>
-  <si>
-    <t>1980000:20</t>
-  </si>
-  <si>
-    <t>1980000:40</t>
-  </si>
-  <si>
-    <t>1980000:80</t>
+    <t>initialPrice</t>
+  </si>
+  <si>
+    <t>client</t>
+  </si>
+  <si>
+    <t>1980000:0</t>
   </si>
   <si>
     <t>1020001:1</t>
@@ -132,13 +156,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -296,12 +326,24 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -628,76 +670,70 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -706,10 +742,10 @@
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -718,10 +754,10 @@
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -730,10 +766,10 @@
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -742,10 +778,10 @@
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -754,21 +790,33 @@
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1082,15 +1130,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="13.75" customWidth="1"/>
     <col min="4" max="4" width="15.75" customWidth="1"/>
     <col min="5" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1106,167 +1155,205 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="4" ht="16.5" spans="1:6">
+      <c r="F4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="4">
         <v>2</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="4">
         <v>60</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2"/>
+      <c r="D5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4">
+        <v>100</v>
+      </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>2</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="4">
         <v>2</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="4">
         <v>120</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="2"/>
+      <c r="D6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4">
+        <v>180</v>
+      </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>3</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="4">
         <v>2</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="4">
         <v>240</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="2"/>
+      <c r="D7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4">
+        <v>320</v>
+      </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>4</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="4">
         <v>480</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4">
+        <v>560</v>
+      </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>17</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="5">
         <v>1</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
         <v>60</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="D9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>15</v>
       </c>
+      <c r="F9" s="5">
+        <v>100</v>
+      </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>18</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="5">
         <v>1</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>120</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="D10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>16</v>
       </c>
+      <c r="F10" s="5">
+        <v>180</v>
+      </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>19</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="5">
         <v>1</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>240</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="D11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="F11" s="5">
+        <v>320</v>
+      </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>20</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="5">
         <v>1</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>480</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="5" t="s">
         <v>18</v>
+      </c>
+      <c r="F12" s="5">
+        <v>560</v>
       </c>
     </row>
   </sheetData>
